--- a/legal_benchmark_examples.xlsx
+++ b/legal_benchmark_examples.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,20 +424,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Case Number (Cause Num)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Court Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Justice Kind</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Generated Question</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Document URL</t>
         </is>
@@ -451,20 +456,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>240/19237/23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/83844d68f7a13a7c369b79daae80a6b0.rtf</t>
         </is>
@@ -478,20 +488,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>752/22764/24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Чи можливий розгляд справи про домашнє насильство за відсутності особи, яка належно повідомлена про засідання?</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/c5f8db8407f54b67c139c78a47bb6f1f.rtf</t>
         </is>
@@ -505,20 +520,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>320/24247/24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню рішення у справах про реєстрацію податкових накладних, розглянутих у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/094c8c37cdfe32599279b7f3e9f3c6f7.rtf</t>
         </is>
@@ -532,20 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>752/17255/24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Чи підлягають стягненню як додаткові витрати на дитину кошти за спортивні секції, табори та одяг?</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/f1b84bbf68f96ea8b674518544b2d1c7.rtf</t>
         </is>
@@ -559,20 +584,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>160/14419/24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Чи зобов'язаний орган влади створювати нову інформацію у відповідь на звернення громадян згідно із законом?</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/2317d3b54d100df33be298ee977b8901.rtf</t>
         </is>
@@ -586,20 +616,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>990/408/24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Які вимоги до змісту позовної заяви при оскарженні рішень ВРП щодо зміни територіальної підсудності справ?</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/60d2dd84e6e72d89bd848511ab8d8e21.rtf</t>
         </is>
@@ -613,20 +648,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>380/1627/24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про перерахунок грошового забезпечення військовослужбовця, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6b85d2dd7cf6dc135a9aef9556c8c787.rtf</t>
         </is>
@@ -640,20 +680,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>320/9156/23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8703c1e23f9f5f7f2fc5367dfcd2b384.rtf</t>
         </is>
@@ -667,20 +712,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>320/24591/23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню рішення у справах про реєстрацію податкових накладних, розглянутих у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/f44cb75e4d1e100872025f1d19b93535.rtf</t>
         </is>
@@ -694,20 +744,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>280/9312/23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про скасування вимоги про сплату недоїмки з єдиного внеску?</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/68858a64884f106d2b531922ab02471b.rtf</t>
         </is>
@@ -721,20 +776,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>160/14516/24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Чи можна оскаржити в касації ухвалу про відмову у відстроченні судового збору та повернення апеляційної скарги?</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/385ebd3bce69c8c86df7c5751bc7cf41.rtf</t>
         </is>
@@ -748,20 +808,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>120/1179/24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій за правилами спрощеного провадження?</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/c7cdfbb7526df1f39f263e9b9559cb56.rtf</t>
         </is>
@@ -775,20 +840,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>380/25868/23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню рішення у справах незначної складності щодо перерахунку грошового забезпечення військовослужбовців?</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/80116877e8f16315dedbb45119934742.rtf</t>
         </is>
@@ -802,20 +872,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>520/11521/23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню рішення у справах незначної складності, розглянутих у спрощеному провадженні, без обґрунтування фундаментального значення?</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/e0799e4f6ba0c41e6857da11b7474ecd.rtf</t>
         </is>
@@ -829,20 +904,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>120/16755/23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про середній заробіток при звільненні, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/7322b323b04a604dc4cfad63c2cb5931.rtf</t>
         </is>
@@ -856,20 +936,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>990/407/24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Чи підлягає оскарженню в адміністративному суді рішення Дорадчої групи експертів щодо оцінювання кандидатів на посаду судді КСУ?</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8764b11eeacd57da57e1dcf025994441.rtf</t>
         </is>
@@ -883,20 +968,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>320/33161/23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення суду у справі про перерахунок суддівської винагороди, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/b725edbda5248da8a55bf76a111b64dc.rtf</t>
         </is>
@@ -910,20 +1000,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>320/18656/23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/db9d0ec3d2fb78bfc4e9faac9b9da798.rtf</t>
         </is>
@@ -937,20 +1032,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>280/9045/24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню ухвали суду першої інстанції після їх перегляду в апеляційному порядку?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/4e9d2e529a930aea579cf6e6bf07cc78.rtf</t>
         </is>
@@ -964,20 +1064,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>480/10667/23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>4851</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Як повернути судовий збір, якщо апеляційну скаргу було повернуто заявнику без розгляду?</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/b9d8bd5992e9ad1f1d4e39a94bf74e2d.rtf</t>
         </is>
@@ -991,20 +1096,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>440/2708/24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Чи підлягає касаційному оскарженню рішення суду у справі про виключення платника податків з переліку ризикових?</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/82b62c1b82b7dac81de8dbc34f3250a5.rtf</t>
         </is>
@@ -1018,20 +1128,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>753/25432/24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>2602</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Чи можливо зупинити виконання розпорядження про надання житла, якщо воно вже фактично виконане вселенням осіб?</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/d41b5860c6c12c67bb0a3159ace2bc10.rtf</t>
         </is>
@@ -1045,20 +1160,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>754/18105/24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>2603</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Як розрахувати судовий збір при поєднанні вимог про визнання права власності та скасування реєстраційних дій нотаріуса?</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/4ca88f2d0722cd05c35d58a900b25577.rtf</t>
         </is>
@@ -1072,20 +1192,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>990/3/24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>9921</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Які підстави для повернення заяви про забезпечення позову без розгляду через недотримання вимог КАС України?</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/fe6d58c54679aeda994572f614806a2a.rtf</t>
         </is>
@@ -1099,20 +1224,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>216/4675/23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Чи правомірне нарахування відсотків після закінчення строку кредиту за відсутності доказів пролонгації електронного договору?</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/3b4659a47951d8a65742386b0a67b68a.rtf</t>
         </is>
@@ -1126,20 +1256,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>562/3361/23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Які підстави та процедура встановлення строку дії рішення про визнання фізичної особи недієздатною?</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/943d9fcde8a63f62e5433dffc3cf9523.rtf</t>
         </is>
@@ -1153,20 +1288,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>752/17547/24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Який порядок стягнення аліментів на повнолітню дитину, яка навчається, та чи підлягають стягненню додаткові витрати на навчання?</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/d558ec412f3e56942064c4ae5f3bd4f4.rtf</t>
         </is>
@@ -1180,20 +1320,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>760/19662/24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>2609</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Чи є підставою для закриття справи про порушення митних правил незабезпечення іноземцю перекладача під час складання протоколу?</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/03f3f8da12484a03a78575159cea0109.rtf</t>
         </is>
@@ -1207,20 +1352,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>607/25495/23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>4817</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Чи можливо витребувати нерухомість від добросовісного набувача, якщо первісний інвестор не виконав умови договору пайової участі?</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/7a3012f5722675b2786af2da774ee50d.rtf</t>
         </is>
@@ -1234,20 +1384,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>753/18042/24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>2602</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Підстави для переходу зі спрощеного провадження до розгляду справи з викликом сторін у кредитних спорах</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/7de4967c94b84bc69463ac425bad588b.rtf</t>
         </is>
@@ -1261,20 +1416,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>910/15556/24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Наслідки неподання видаткової накладної до позовної заяви про стягнення заборгованості за договором поставки</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8b8e886d0533f90ac09eaeb57e211633.rtf</t>
         </is>
@@ -1288,20 +1448,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>753/12170/24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Чи можливий перехід зі спрощеного до загального провадження при необхідності призначення почеркознавчої експертизи договору?</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/efb2c07970b2167e6bb0c0b9bbc2f23b.rtf</t>
         </is>
@@ -1315,20 +1480,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>910/9486/24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>4873</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Які наслідки подання апеляційної скарги після строку без клопотання про його поновлення в господарському процесі?</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/af3b3cc2b9821aa1c62c1ebef4716183.rtf</t>
         </is>
@@ -1342,20 +1512,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>910/8792/24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>4873</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Який порядок розрахунку судового збору за подання апеляційної скарги у господарському процесі при оскарженні рішення суду?</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/eb054c267e54fb5c48e94005e26b6776.rtf</t>
         </is>
@@ -1369,20 +1544,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>755/22180/24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2604</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Які підстави та порядок застосування приводу особи у справах про адміністративні правопорушення за статтею 173 КУпАП?</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/23d411d1c9f65f2c751308788e7e250e.rtf</t>
         </is>
@@ -1396,20 +1576,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>908/1634/24(908/2316/24)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>5009</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Чи підлягає стягненню заборгованість в іноземній валюті з фізичної особи на користь юридичної особи?</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/101a6415c3099e65555f43a7d6ab1d3a.rtf</t>
         </is>
@@ -1423,20 +1608,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>755/22200/24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2604</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Які підстави та процедура застосування приводу особи у справах про адміністративні правопорушення з обов'язковою присутністю?</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/dc5c65c5e3197592765cb706611f01fb.rtf</t>
         </is>
@@ -1450,20 +1640,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>758/11830/17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>4824</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Чи є проживання дітей з одним із подружжя достатньою підставою для відступу від рівності часток при поділі авто?</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/f182f79b7cb2ef228048f4a77c181942.rtf</t>
         </is>
@@ -1477,20 +1672,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>910/16110/24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Чи можливо зобов'язати реєстратора переделегувати доменне ім'я після визнання недійсним договору про передачу прав на торговельну марку?</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6f5c6d6ad0888b77013270297a1691a3.rtf</t>
         </is>
@@ -1504,20 +1704,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>910/15411/24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Чи правомірне застосування тарифів для промисловості до колективного споживача послуг водопостачання при відсутності укладеного договору?</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/534b17d8b316cff74f38d0ddde7edc9f.rtf</t>
         </is>
@@ -1531,20 +1736,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>910/12861/24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Чи обов'язковий виклик сторін при розгляді заяви про ухвалення додаткового рішення щодо судових витрат?</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/3c40d62596acb31f305b30570900a070.rtf</t>
         </is>
@@ -1558,20 +1768,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>755/21591/24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2604</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Чи є підставою для закриття справи про адмінправопорушення невідповідність протоколу вимогам ст. 256 КУпАП?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/82fb4a38bf58e8c6d92c986629d4323b.rtf</t>
         </is>
@@ -1585,20 +1800,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>910/15084/24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Чи підлягає зупиненню господарська справа про відшкодування збитків до вирішення адміністративного спору щодо податкового повідомлення-рішення?</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/08f8c43848168682f83d30fe578922f8.rtf</t>
         </is>
@@ -1612,20 +1832,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>910/16053/24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Як стягнути кошти з Укрзалізниці шляхом зобов'язання внести зміни до особового рахунку клієнта?</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/98c4a12f8a169de6d3b35dd9a4616fdb.rtf</t>
         </is>
@@ -1639,20 +1864,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>910/16056/24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Чи можна через суд зобов'язати залізницю відновити грошові кошти на особовому рахунку клієнта?</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/ec8808498477923c2efa462cb00509d2.rtf</t>
         </is>
@@ -1666,20 +1896,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>910/14329/24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Чи є картка рахунку належним доказом виконання робіт за договором підряду за відсутності підписаного акту?</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/e933885ff484c7c8d4fe284d0f903f93.rtf</t>
         </is>
@@ -1693,20 +1928,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>761/4385/20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Підстави для відмови у задоволенні скарги на бездіяльність державного виконавця щодо вчинення виконавчих дій</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/68d183bb56e8166f5dded110133ceae9.rtf</t>
         </is>
@@ -1720,20 +1960,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>752/25338/24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Чи можливе встановлення обопільної вини водіїв у ДТП при порушенні правил безпечного бокового інтервалу?</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/b9bc591b5b5bdaacb40a28f0bee8922a.rtf</t>
         </is>
@@ -1747,20 +1992,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>761/42085/19</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>чи можливе ухвалення додаткового рішення суду, якщо питання розподілу судових витрат не було вирішено в основному рішенні?</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6954d18de37e51a270d2a9e29cdee507.rtf</t>
         </is>
@@ -1774,20 +2024,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>752/26535/24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Відповідальність за створення перешкод дорожньому руху під час виконання будівельних робіт спецтехнікою</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6a942e3560e7a1d87ab79b24298aac96.rtf</t>
         </is>
@@ -1801,20 +2056,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>761/30647/23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Чи підлягає прийняттю зустрічний позов про поділ спільного майна подружжя у справі про спадкування?</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8d3c40241aa64328cd9597b87dd4fad8.rtf</t>
         </is>
@@ -1828,20 +2088,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>761/42312/24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Чи підлягає поверненню позовна заява за клопотанням позивача до відкриття провадження у справі?</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/3d5404492db5850ed54cf1f782e9a998.rtf</t>
         </is>
@@ -1855,20 +2120,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>368/1155/23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>9931</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню рішення у справах про стягнення аліментів на утримання непрацездатних батьків?</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/06ada10a11ae475576fb35ace1ff9b97.rtf</t>
         </is>
@@ -1882,20 +2152,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>225/3164/21</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>9931</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Чи підлягають касаційному оскарженню судові рішення у справах про звільнення від сплати аліментів?</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/484f25a93a356bf48acf7bad06e9463c.rtf</t>
         </is>
@@ -1909,20 +2184,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>752/25975/24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Відповідальність за ст. 124 КУпАП при наїзді на припарковане авто під час руху заднім ходом</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/c443068c94e59b9500d70dbd3bb46566.rtf</t>
         </is>
@@ -1936,20 +2216,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>908/2123/23(908/3031/24)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>5009</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Чи підлягає позов про скасування реєстрації іпотеки розгляду в межах справи про банкрутство боржника?</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/95d537fabbe1693e1fc1e4324b36f1e8.rtf</t>
         </is>
@@ -1963,20 +2248,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>758/4169/24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Як зупинити стягнення за виконавчим написом нотаріуса шляхом забезпечення позову про визнання його таким, що не підлягає виконанню?</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/17a4340917c4eaf2d7d665cf7e462e91.rtf</t>
         </is>
@@ -1990,20 +2280,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>530/2691/24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>1607</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Який порядок визнання права на земельну частку (пай) у судовому порядку після смерті власника?</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/eab7b6e450f8cbb8efb79a7f965f6787.rtf</t>
         </is>
@@ -2017,20 +2312,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>530/2537/24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>1607</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Які процесуальні наслідки неподання відповідачем відзиву на позов у встановлений судом строк?</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/0d012e4e17152fc85f7d6d19d13ec765.rtf</t>
         </is>
@@ -2044,20 +2344,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>635/11525/23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2610</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>civil</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Який порядок заміни стягувача у виконавчому провадженні на підставі договору відступлення права вимоги?</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/deaf3e0bd5718f657d0a32a37a83b1e8.rtf</t>
         </is>
@@ -2071,20 +2376,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>753/7823/24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2602</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Яка відповідальність за порушення правил адміністративного нагляду, зокрема відвідування закладів, де продають алкоголь?</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/2ce84ef001bf9bb98ddfcd550a207795.rtf</t>
         </is>
@@ -2098,20 +2408,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>752/24822/24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Відповідальність за ст. 124 КУпАП при ДТП під час руху заднім ходом без забезпечення безпеки маневру</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/dd9c4284d2938a93630cd2535a7751b1.rtf</t>
         </is>
@@ -2125,20 +2440,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>752/21839/24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2601</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Чи можливий розгляд справи про порушення порядку розрахунків за ст. 155-1 КУпАП без присутності продавця?</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/ca9ca5715c2ff054048ca85a0001ed89.rtf</t>
         </is>
@@ -2152,20 +2472,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>910/9177/24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>4873</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Який розмір судового збору за подання апеляційної скарги через Електронний суд у господарському процесі?</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/2850395cf0febfd314cfef08ed8d0d2f.rtf</t>
         </is>
@@ -2179,20 +2504,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>518/2358/24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>1532</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Чи є підставою для відповідальності за ст. 184 КУпАП травмування дитини через відсутність нагляду батьків?</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/9867d55101cf900f81aa75ecdcd62a9d.rtf</t>
         </is>
@@ -2206,20 +2536,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>522/23352/24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>1522</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Чи є правомірним розірвання договору в односторонньому порядку без попереднього письмового повідомлення іншої сторони?</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6559746e5e8ff24608835cd1b1d8aa2c.rtf</t>
         </is>
@@ -2233,20 +2568,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>607/26310/24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Які докази є достатніми для притягнення до відповідальності за психологічне домашнє насильство без фізичних ушкоджень?</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/89b8a899c0afdfc1e685cc560f0f93ca.rtf</t>
         </is>
@@ -2260,20 +2600,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>466/884/24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Чи підлягають об'єднанню в одне провадження справи за ст. 124 та ст. 130 КУпАП?</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/31eca50bc5eaa7740d92818063aff901.rtf</t>
         </is>
@@ -2287,20 +2632,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>759/11610/23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>4824</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>процесуальний порядок призначення апеляційного розгляду після відкриття провадження за скаргою обвинуваченого</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/6759bffee8ed5e0f4ab1f5976a1e1798.rtf</t>
         </is>
@@ -2314,20 +2664,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>563/2123/24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>1709</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Чи можливо виправити технічну описку в резолютивній частині вироку щодо кваліфікації кримінального правопорушення?</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/75941496c352a5b3d81f98a0b5b0972c.rtf</t>
         </is>
@@ -2341,20 +2696,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>760/24553/24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>4824</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>процесуальний порядок призначення апеляційного розгляду кримінального провадження за ч 4 ст 191 КК України</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/df07abcb4b03f8c23995b9e8d4954f71.rtf</t>
         </is>
@@ -2368,20 +2728,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>569/25409/24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Чи обов'язкове підготовче засідання, якщо в обвинувальному акті щодо кримінального проступку відсутнє клопотання про спрощений розгляд?</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/19c1052c81bf7c16d165b59e15d34b8e.rtf</t>
         </is>
@@ -2395,20 +2760,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>554/13052/24</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>1622</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Які підстави для накладення арешту на тимчасово вилучене майно як речовий доказ у кримінальному провадженні?</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/e638cfcb161ba08c5bfa9cbde01a60fb.rtf</t>
         </is>
@@ -2422,20 +2792,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>569/18131/24</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Як застосувати закон про декриміналізацію дрібних крадіжок до вироку, якщо вартість майна не перевищує 2 неоподатковуваних мінімумів?</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/a117ff8151cf2afa2fc86cda4e5138b4.rtf</t>
         </is>
@@ -2449,20 +2824,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>357/5072/23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Звільнення від покарання за крадіжку у зв'язку з декриміналізацією дрібних крадіжок за законом № 3886-IX?</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/a8b860ddb5d12c84febc5aeb1fe17997.rtf</t>
         </is>
@@ -2476,20 +2856,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>552/9020/24</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Які критерії визначення розміру застави для підозрюваного у тяжкому злочині, якщо захист не надав доказів майнової неспроможності?</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/befdb1b01807b51e515ece5e8e457ef4.rtf</t>
         </is>
@@ -2503,20 +2888,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>569/13624/23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Як виключити епізод крадіжки з вироку через декриміналізацію дрібних крадіжок згідно із Законом № 3886-IX?</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/afa65b8b5a12383eb06f639bd63fe21d.rtf</t>
         </is>
@@ -2530,20 +2920,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>569/14919/19</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Як звільнити засудженого від покарання за крадіжку через декриміналізацію діяння згідно із законом № 3886-ІХ?</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/0f02aa3fc493058a1c11f0e5b1c73d1e.rtf</t>
         </is>
@@ -2557,20 +2952,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>695/3390/23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Як переглянути вирок через декриміналізацію крадіжки після підвищення порогу кримінальної відповідальності за дрібне викрадення?</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/39a30ed741d6dc6fdb8cd82a2c8595ba.rtf</t>
         </is>
@@ -2584,20 +2984,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>201/16320/24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Підстави для відмови слідчого судді у застосуванні запобіжного заходу у вигляді тримання під вартою</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8b5de4336313d3756e4f886f317182fd.rtf</t>
         </is>
@@ -2611,20 +3016,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>127/40798/24</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Підстави для відмови у застосуванні тримання під вартою за підозрою у вимаганні за ч. 4 ст. 189 КК</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/d792902f507bdec0583bde37f173d1d3.rtf</t>
         </is>
@@ -2638,20 +3048,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>556/3606/24</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Чи можна виділити матеріали кримінального провадження в окреме провадження, якщо угоду про визнання винуватості укладено лише з одним обвинуваченим?</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/89ec046f49b00f206f6bf433f193e427.rtf</t>
         </is>
@@ -2665,20 +3080,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>426/2628/14-к</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>1609</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Чи є обов'язковою участь захисника при розгляді заяви про продовження примусових заходів медичного характеру?</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/d79c8ee9f62c73a7236de400dddc009e.rtf</t>
         </is>
@@ -2692,20 +3112,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>638/4213/24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>процедура оскарження постанови слідчого про закриття кримінального провадження та витребування матеріалів справи</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/62f176866bdae64ba228a24f7c189a1d.rtf</t>
         </is>
@@ -2719,20 +3144,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>569/17179/19</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Як привести вирок у відповідність до закону, якщо крадіжка декриміналізована через підвищення порогу дрібного викрадення?</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/22846628bce0c9c220e3d4235c4f46c7.rtf</t>
         </is>
@@ -2746,20 +3176,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>208/14301/24</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>415</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Чи можна накласти арешт на вилучений речовий доказ із передачею права користування власнику?</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/a17a1588ce04120e57d5e3c22f7c6811.rtf</t>
         </is>
@@ -2773,20 +3208,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>607/27552/24</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Чи можливо визначити заставу при продовженні тримання під вартою у справах про наркозлочини в складі організованої групи?</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/79f4f0f00dad11331e18822a9c3c03dd.rtf</t>
         </is>
@@ -2800,20 +3240,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>922/4759/24</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>5023</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Підстави для відмови в арешті частки ТОВ при позові про переведення прав покупця корпоративних прав</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/0bd627bce731cde71bb8ab443dbf4440.rtf</t>
         </is>
@@ -2827,20 +3272,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>922/3672/21</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>5023</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Чи можна виключити частку в статутному капіталі з ліквідаційної маси боржника за ст. 132 КУзПБ?</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/3eb7b812ca12f84eb010391c6e03118b.rtf</t>
         </is>
@@ -2854,20 +3304,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>922/1675/24</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
           <t>4875</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Як правильно розрахувати судовий збір за апеляційну скаргу в справі про банкрутство при подачі через Електронний суд?</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8ef014c9c5c335de8a52e1730ea971b2.rtf</t>
         </is>
@@ -2881,20 +3336,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>925/1240/21</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>5026</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Чи є скасування ухвали суду вищою інстанцією підставою для відводу судді згідно з ГПК України?</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/49741bca89bfeba87a45fae30b9da5da.rtf</t>
         </is>
@@ -2908,20 +3368,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>912/3817/19</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>5013</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Підстави для зупинення провадження у справі до набрання законної сили рішенням в іншій пов'язаній справі</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/c9e1b4f951731ccffefecd23f52d4604.rtf</t>
         </is>
@@ -2935,20 +3400,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>908/3001/24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>5009</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Чи можливо повернутися до підготовчого провадження після його закриття для залучення третьої особи у господарському процесі?</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8fafacf167dcebda85b94ff39458f622.rtf</t>
         </is>
@@ -2962,20 +3432,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>909/171/24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>5010</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>commercial</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Чи є клопотання арбітражного керуючого про відкладення розгляду справи для узгодження плану реструктуризації підставою для відкладення засідання?</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/57dbaea1434495c8f11bf4daac1e0f1f.rtf</t>
         </is>
@@ -2989,20 +3464,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>216/5342/24</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Чи можна поновити провадження у справі про ДТП після надходження висновку судової автотехнічної експертизи?</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/0465308d4fa59918d82f6a4b3056623c.rtf</t>
         </is>
@@ -3016,20 +3496,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>190/2368/24</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Які докази психологічного домашнього насильства є достатніми для притягнення до відповідальності за ст. 173-2 КУпАП?</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/585be447b1c227a99f35b62e771ff353.rtf</t>
         </is>
@@ -3043,20 +3528,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>190/2830/24</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Відповідальність за повторне порушення правил адміністративного нагляду: неявка на реєстрацію до поліції</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/560451aee5cc99139ac8e3e1bbe370a8.rtf</t>
         </is>
@@ -3070,20 +3560,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>286/4354/24</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Підстави та порядок об'єднання кількох справ про адміністративні правопорушення щодо однієї особи в одне провадження</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/5c9a04d184e3d44de9d4a60b3728c46a.rtf</t>
         </is>
@@ -3097,20 +3592,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>564/1593/21</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
           <t>1710</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Чи підлягає закриттю справа про адмінправопорушення за ст. 130 КУпАП після спливу строків накладення стягнення?</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/8c442e2746d71449101f4da547fcf8b0.rtf</t>
         </is>
@@ -3124,20 +3624,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>638/24684/24</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>infraction</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Чи враховуються пом'якшуючі обставини при призначенні штрафу за ст. 124 КУпАП у справах про ДТП?</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>https://od.reyestr.court.gov.ua/files/62/1936ebb5afc7ff7ba6fc33da0a48b17b.rtf</t>
         </is>

--- a/legal_benchmark_examples.xlsx
+++ b/legal_benchmark_examples.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,6 +425,14 @@
   </sheetPr>
   <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -451,17 +469,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>124185776</t>
+          <t>131204357</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>240/19237/23</t>
+          <t>520/29348/24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -469,63 +487,63 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/83844d68f7a13a7c369b79daae80a6b0.rtf</t>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Чи є воєнний стан та розосередження підрозділів поважною причиною для поновлення строку на апеляційне оскарження?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/3c5a475908bee3eac48f864465fb3122.rtf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>124176959</t>
+          <t>128829140</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>752/22764/24</t>
+          <t>520/8013/25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Чи можливий розгляд справи про домашнє насильство за відсутності особи, яка належно повідомлена про засідання?</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/c5f8db8407f54b67c139c78a47bb6f1f.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний ПФУ перерахувати пенсію військовому на підставі оновленої довідки про грошове забезпечення з урахуванням прожиткового мінімуму?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/8b1f9d0f5806d96919171b31055a8229.rtf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>124185778</t>
+          <t>126745773</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>320/24247/24</t>
+          <t>695/1446/25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -533,63 +551,63 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню рішення у справах про реєстрацію податкових накладних, розглянутих у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/094c8c37cdfe32599279b7f3e9f3c6f7.rtf</t>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Який процесуальний порядок розгляду позову про скасування постанови про адміністративне правопорушення в порядку спрощеного провадження?</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/7e09dbf944f7257ee363227e57e5745c.rtf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>124176880</t>
+          <t>124843815</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>752/17255/24</t>
+          <t>600/367/25-а</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Чи підлягають стягненню як додаткові витрати на дитину кошти за спортивні секції, табори та одяг?</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/f1b84bbf68f96ea8b674518544b2d1c7.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Який строк звернення до суду з позовом про оскарження рішення ВЛК щодо придатності до військової служби?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/0e6f30782a9bd9e8c7c235e313cb763b.rtf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>124185770</t>
+          <t>129645652</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160/14419/24</t>
+          <t>440/10568/24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -597,31 +615,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Чи зобов'язаний орган влади створювати нову інформацію у відповідь на звернення громадян згідно із законом?</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/2317d3b54d100df33be298ee977b8901.rtf</t>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Які вимоги до змісту звіту суб'єкта владних повноважень про виконання судового рішення згідно з КАС України?</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/a33803bb198407236a79af60e38af974.rtf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>124185792</t>
+          <t>130216446</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>990/408/24</t>
+          <t>500/3663/25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -629,31 +647,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Які вимоги до змісту позовної заяви при оскарженні рішень ВРП щодо зміни територіальної підсудності справ?</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/60d2dd84e6e72d89bd848511ab8d8e21.rtf</t>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Які вимоги до форми та змісту апеляційної скарги на рішення суду в адміністративній справі?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/494bb2aed0f9c0d203a3b7d5db9491c4.rtf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>124185789</t>
+          <t>127547694</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>380/1627/24</t>
+          <t>140/5481/25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>370</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -661,31 +679,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про перерахунок грошового забезпечення військовослужбовця, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6b85d2dd7cf6dc135a9aef9556c8c787.rtf</t>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Як стягнути перерахунок пенсії чорнобильцям у розмірі десяти мінімальних пенсій за віком?</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/03d316744ffb2185cf19b74697ad320c.rtf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>124185777</t>
+          <t>131303074</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>320/9156/23</t>
+          <t>160/22529/25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -693,31 +711,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8703c1e23f9f5f7f2fc5367dfcd2b384.rtf</t>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>За яких умов апеляційний адміністративний суд розглядає справу в порядку письмового провадження без виклику сторін?</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/3f604df6d2945d93fe8779f18a860f95.rtf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>124185775</t>
+          <t>129970063</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>320/24591/23</t>
+          <t>200/6592/25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>570</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -725,31 +743,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню рішення у справах про реєстрацію податкових накладних, розглянутих у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/f44cb75e4d1e100872025f1d19b93535.rtf</t>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний орган ДПС видавати довідки про заробітну плату для перерахунку пенсії колишньому державному службовцю?</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/9c774bd73c3e979c3a7b60b6aea1453e.rtf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>124185779</t>
+          <t>131327305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280/9312/23</t>
+          <t>440/14409/25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -757,26 +775,26 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про скасування вимоги про сплату недоїмки з єдиного внеску?</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/68858a64884f106d2b531922ab02471b.rtf</t>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Судова практика щодо перерахунку чорнобильської пенсії без застосування двоскладової формули обчислення стажу</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/e9119f79a210d850b91bcfab4cb00881.rtf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>124185793</t>
+          <t>124336900</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160/14516/24</t>
+          <t>520/12300/24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -789,31 +807,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Чи можна оскаржити в касації ухвалу про відмову у відстроченні судового збору та повернення апеляційної скарги?</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/385ebd3bce69c8c86df7c5751bc7cf41.rtf</t>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Як повернути судовий збір після відмови у відкритті касаційного провадження в адміністративній справі?</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/49cf1debd790ffc6041dd7f9a4a4a14a.rtf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>124185771</t>
+          <t>127371986</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>120/1179/24</t>
+          <t>200/690/25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -821,31 +839,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій за правилами спрощеного провадження?</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/c7cdfbb7526df1f39f263e9b9559cb56.rtf</t>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Чи є воєнний стан достатньою підставою для продовження строків розгляду адміністративної справи в апеляційному порядку?</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/89f3004f86bc77589da4d8cfcaa47bd9.rtf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>124185782</t>
+          <t>132900231</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>380/25868/23</t>
+          <t>500/6762/25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -853,31 +871,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню рішення у справах незначної складності щодо перерахунку грошового забезпечення військовослужбовців?</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/80116877e8f16315dedbb45119934742.rtf</t>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний ПФУ перерахувати військову пенсію на підставі оновленої довідки про грошове забезпечення з урахуванням премій?</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/f81b1c07d43973f8f8cf4a49cb714a5e.rtf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>124185773</t>
+          <t>125445363</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>520/11521/23</t>
+          <t>400/7022/24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -885,31 +903,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню рішення у справах незначної складності, розглянутих у спрощеному провадженні, без обґрунтування фундаментального значення?</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/e0799e4f6ba0c41e6857da11b7474ecd.rtf</t>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягає компенсації втрата частини індексації грошового забезпечення військовослужбовця за весь період затримки виплати, а не лише з моменту звернення до суду?</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/9e9d3cf9c4522e7c95e8cc875d531190.rtf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>124185781</t>
+          <t>126993581</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>120/16755/23</t>
+          <t>440/5639/25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -917,31 +935,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про середній заробіток при звільненні, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/7322b323b04a604dc4cfad63c2cb5931.rtf</t>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Яка судова практика щодо відмови ПФУ у перерахунку пенсії при переході на пенсію у зв'язку з втратою годувальника?</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/75ca4fb2d2c1be9896a9a0fdb85a201f.rtf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>124185791</t>
+          <t>127166132</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>990/407/24</t>
+          <t>560/3854/25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -949,31 +967,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Чи підлягає оскарженню в адміністративному суді рішення Дорадчої групи експертів щодо оцінювання кандидатів на посаду судді КСУ?</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8764b11eeacd57da57e1dcf025994441.rtf</t>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Як зобов'язати орган видати довідку про грошове забезпечення з урахуванням прожиткового мінімуму для перерахунку військової пенсії?</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/e71f2781444ccc039cfc912f3ece8e82.rtf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>124185790</t>
+          <t>131044721</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>320/33161/23</t>
+          <t>400/1788/24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -981,31 +999,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення суду у справі про перерахунок суддівської винагороди, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/b725edbda5248da8a55bf76a111b64dc.rtf</t>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягає виплаті учасникам бойових дій щорічна грошова допомога до Дня Незалежності у розмірі п'яти мінімальних пенсій?</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/68a41e3232c2e46356339a072ed40edc.rtf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>124185774</t>
+          <t>130476753</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>320/18656/23</t>
+          <t>580/5726/25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1013,31 +1031,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення у справі про реєстрацію податкових накладних, розглянутій у спрощеному провадженні?</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/db9d0ec3d2fb78bfc4e9faac9b9da798.rtf</t>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Підстави для продовження строків апеляційного розгляду адміністративної справи в умовах воєнного стану</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/f2c99ae2f705695f3851e947a79e8183.rtf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>124185785</t>
+          <t>131661367</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280/9045/24</t>
+          <t>380/21853/25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1045,31 +1063,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню ухвали суду першої інстанції після їх перегляду в апеляційному порядку?</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/4e9d2e529a930aea579cf6e6bf07cc78.rtf</t>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний орган скласти довідку про грошове забезпечення військового пенсіонера з урахуванням прожиткового мінімуму поточного року?</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/fc65fb4ae95cf16ed3fc918e2c107b4b.rtf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>124184030</t>
+          <t>130666520</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>480/10667/23</t>
+          <t>140/1696/25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1077,31 +1095,31 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Як повернути судовий збір, якщо апеляційну скаргу було повернуто заявнику без розгляду?</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/b9d8bd5992e9ad1f1d4e39a94bf74e2d.rtf</t>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Підстави для звільнення ФОП від сплати адміністративно-господарських санкцій за невиконання нормативу робочих місць для осіб з інвалідністю.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/d2b272d69f87fc6e2f5229002d3ae52e.rtf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>124185784</t>
+          <t>130663099</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>440/2708/24</t>
+          <t>440/9614/25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1109,735 +1127,735 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Чи підлягає касаційному оскарженню рішення суду у справі про виключення платника податків з переліку ризикових?</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/82b62c1b82b7dac81de8dbc34f3250a5.rtf</t>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Чи звільняється військова частина від сплати судового збору при поданні апеляційної скарги в адміністративній справі?</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/3f22fdc31e7db4d0cba3a8c43c203ee5.rtf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>124177021</t>
+          <t>129631882</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>753/25432/24</t>
+          <t>906/1065/25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Чи можливо зупинити виконання розпорядження про надання житла, якщо воно вже фактично виконане вселенням осіб?</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/d41b5860c6c12c67bb0a3159ace2bc10.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки подання позову через Електронний суд без доказів направлення документів відповідачу та сплати судового збору?</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/7b427336e00f75b87ec9f3da3945516f.rtf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>124177025</t>
+          <t>129182638</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>754/18105/24</t>
+          <t>925/1577/20(925/147/23)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Як розрахувати судовий збір при поєднанні вимог про визнання права власності та скасування реєстраційних дій нотаріуса?</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/4ca88f2d0722cd05c35d58a900b25577.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягають скасуванню заходи забезпечення позову після зміни способу виконання рішення суду на стягнення грошових коштів?</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/9336d8dddbe1e70799d748d7865c3508.rtf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>124185769</t>
+          <t>127246885</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>990/3/24</t>
+          <t>914/1895/24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Які підстави для повернення заяви про забезпечення позову без розгляду через недотримання вимог КАС України?</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/fe6d58c54679aeda994572f614806a2a.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки залишення апеляційної скарги без руху через відсутність доказів сплати судового збору та електронного кабінету?</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/d60a266de8775d2555b02e6b14d6350d.rtf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>124176192</t>
+          <t>125875774</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>216/4675/23</t>
+          <t>922/4135/24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Чи правомірне нарахування відсотків після закінчення строку кредиту за відсутності доказів пролонгації електронного договору?</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/3b4659a47951d8a65742386b0a67b68a.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Який порядок стягнення АМКУ штрафу та пені за порушення законодавства про захист економічної конкуренції в судовому порядку?</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/0fc0dd953c445ba50234170ff60aab0d.rtf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>124176461</t>
+          <t>132404262</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>562/3361/23</t>
+          <t>520/5002/25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Які підстави та процедура встановлення строку дії рішення про визнання фізичної особи недієздатною?</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/943d9fcde8a63f62e5433dffc3cf9523.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Чи є введення воєнного стану достатньою підставою для поновлення строку на апеляційне оскарження державним органом?</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/c6af957cc8f65f4c685d208552436c78.rtf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>124176879</t>
+          <t>127516467</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>752/17547/24</t>
+          <t>440/3128/25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Який порядок стягнення аліментів на повнолітню дитину, яка навчається, та чи підлягають стягненню додаткові витрати на навчання?</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/d558ec412f3e56942064c4ae5f3bd4f4.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Чи потрібно надсилати копію апеляційної скарги поштою, якщо вона подана через систему Електронний суд?</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/e36254db0053485993e042a976613138.rtf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>124177152</t>
+          <t>131858890</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>760/19662/24</t>
+          <t>320/54072/25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Чи є підставою для закриття справи про порушення митних правил незабезпечення іноземцю перекладача під час складання протоколу?</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/03f3f8da12484a03a78575159cea0109.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Як зобов'язати ТЦК видати довідку про грошове забезпечення для перерахунку пенсії з урахуванням прожиткового мінімуму 2023 року?</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/1f3330ec1c2713a200d11b88e4734357.rtf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>124187043</t>
+          <t>132409368</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>607/25495/23</t>
+          <t>380/12495/25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Чи можливо витребувати нерухомість від добросовісного набувача, якщо первісний інвестор не виконав умови договору пайової участі?</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/7a3012f5722675b2786af2da774ee50d.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Чи застосовується коефіцієнт 0,8 при сплаті судового збору за подання апеляції через систему Електронний суд?</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/c46f7933a2ae40c613bd16ded3d3d744.rtf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>124176987</t>
+          <t>128355446</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>753/18042/24</t>
+          <t>120/2458/25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Підстави для переходу зі спрощеного провадження до розгляду справи з викликом сторін у кредитних спорах</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/7de4967c94b84bc69463ac425bad588b.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірне нарахування штрафів та пені за несплату ЄСВ у період дії воєнного стану?</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/b09fa3950e8a6071461b0d366fa90921.rtf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>124185359</t>
+          <t>126340674</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>910/15556/24</t>
+          <t>420/9349/25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Наслідки неподання видаткової накладної до позовної заяви про стягнення заборгованості за договором поставки</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8b8e886d0533f90ac09eaeb57e211633.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Як оскаржити відмову уповноваженого органу у видачі довідки про грошове забезпечення для перерахунку військової пенсії?</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/4894fcb06b3fd5c01c318d113d780f14.rtf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>124176881</t>
+          <t>124406084</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>753/12170/24</t>
+          <t>520/7422/24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Чи можливий перехід зі спрощеного до загального провадження при необхідності призначення почеркознавчої експертизи договору?</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/efb2c07970b2167e6bb0c0b9bbc2f23b.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Як обґрунтувати виняткові підстави для касаційного оскарження у справі незначної складності в адміністративному процесі?</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/d7892dea7579bb1f0a386a78d2b6e167.rtf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>124185070</t>
+          <t>129592990</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>910/9486/24</t>
+          <t>300/2904/22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Які наслідки подання апеляційної скарги після строку без клопотання про його поновлення в господарському процесі?</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/af3b3cc2b9821aa1c62c1ebef4716183.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягають касаційному оскарженню рішення щодо перерахунку індексації грошового забезпечення військовослужбовців у справах незначної складності?</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/96b87d3795a6b374b1e2c231d1b7a65c.rtf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>124185072</t>
+          <t>128948944</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>910/8792/24</t>
+          <t>560/11845/25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Який порядок розрахунку судового збору за подання апеляційної скарги у господарському процесі при оскарженні рішення суду?</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/eb054c267e54fb5c48e94005e26b6776.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Які поважні причини пропуску строку звернення до суду щодо оскарження припинення виплати пенсії Пенсійним фондом?</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/4017250f7715ade05f9e16170820641a.rtf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>124177044</t>
+          <t>127337452</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>755/22180/24</t>
+          <t>340/1560/23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Які підстави та порядок застосування приводу особи у справах про адміністративні правопорушення за статтею 173 КУпАП?</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/23d411d1c9f65f2c751308788e7e250e.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Чи можна змінити спосіб виконання рішення суду на стягнення коштів у спорах з Пенсійним фондом?</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/63b33c7d3f7c838c6b828c7588141902.rtf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>124185281</t>
+          <t>132727714</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>908/1634/24(908/2316/24)</t>
+          <t>420/29747/24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Чи підлягає стягненню заборгованість в іноземній валюті з фізичної особи на користь юридичної особи?</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/101a6415c3099e65555f43a7d6ab1d3a.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Чи є лист Пенсійного фонду з розрахунком пенсії початком відліку строку звернення до суду?</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/15c829e89d7cf29c3035416cc490ab0c.rtf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>124177043</t>
+          <t>128704998</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>755/22200/24</t>
+          <t>160/7277/25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Які підстави та процедура застосування приводу особи у справах про адміністративні правопорушення з обов'язковою присутністю?</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/dc5c65c5e3197592765cb706611f01fb.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Які докази майнового стану є достатніми для звільнення фізичної особи від сплати судового збору в апеляції?</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/60cc210ae1d015adca92c49191b13a45.rtf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>124177978</t>
+          <t>124354633</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>758/11830/17</t>
+          <t>158/78/25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Чи є проживання дітей з одним із подружжя достатньою підставою для відступу від рівності часток при поділі авто?</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/f182f79b7cb2ef228048f4a77c181942.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Які підстави для відмови у продовженні строку затримання іноземця з метою примусового видворення?</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/a6b17be1caaaf796c158ca765170f9d4.rtf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>124185389</t>
+          <t>125615459</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>910/16110/24</t>
+          <t>320/8786/25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Чи можливо зобов'язати реєстратора переделегувати доменне ім'я після визнання недійсним договору про передачу прав на торговельну марку?</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6f5c6d6ad0888b77013270297a1691a3.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягають позови до Пенсійного фонду про зобов'язання вчинити дії розгляду в порядку спрощеного провадження?</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/bd8a1a98cb778a9616649c4232211ac4.rtf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>124185363</t>
+          <t>127972538</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>910/15411/24</t>
+          <t>140/5968/25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>370</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Чи правомірне застосування тарифів для промисловості до колективного споживача послуг водопостачання при відсутності укладеного договору?</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/534b17d8b316cff74f38d0ddde7edc9f.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Як усунути невідповідність між відповідачем у позові та органом, що прийняв оскаржуване рішення Пенсійного фонду?</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/34764102f4aa12ef7be4c2d819918bee.rtf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>124185379</t>
+          <t>132695198</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>910/12861/24</t>
+          <t>140/10030/25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>370</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Чи обов'язковий виклик сторін при розгляді заяви про ухвалення додаткового рішення щодо судових витрат?</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/3c40d62596acb31f305b30570900a070.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний ПФУ здійснити перерахунок військової пенсії на підставі оновленої довідки про грошове забезпечення?</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/fde274fb96b3930fd9f4a2df948c615a.rtf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>124177032</t>
+          <t>127230552</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>755/21591/24</t>
+          <t>320/22434/25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Чи є підставою для закриття справи про адмінправопорушення невідповідність протоколу вимогам ст. 256 КУпАП?</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/82fb4a38bf58e8c6d92c986629d4323b.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірне обмеження максимального розміру пенсії десятьма прожитковими мінімумами при її перерахунку?</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/7e49a8e00b75a35394df79445fb8a42d.rtf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>124185372</t>
+          <t>130620352</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>910/15084/24</t>
+          <t>560/17438/24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Чи підлягає зупиненню господарська справа про відшкодування збитків до вирішення адміністративного спору щодо податкового повідомлення-рішення?</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/08f8c43848168682f83d30fe578922f8.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Як довести право на виплату 100 тисяч грн, якщо військовий був у відрядженні в іншій частині?</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/46420be07ab98b84120764df702e3eb4.rtf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>124185394</t>
+          <t>128719931</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>910/16053/24</t>
+          <t>920/570/23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1845,31 +1863,31 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Як стягнути кошти з Укрзалізниці шляхом зобов'язання внести зміни до особового рахунку клієнта?</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/98c4a12f8a169de6d3b35dd9a4616fdb.rtf</t>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Як розрахувати судовий збір за апеляційну скаргу, що містить як майнові, так і немайнові вимоги?</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/b8e387d3487e3bc771052e5027a40e2b.rtf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>124185395</t>
+          <t>131455291</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>910/16056/24</t>
+          <t>911/1727/24 (361/2603/25)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1877,31 +1895,31 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Чи можна через суд зобов'язати залізницю відновити грошові кошти на особовому рахунку клієнта?</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/ec8808498477923c2efa462cb00509d2.rtf</t>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягають передачі до господарського суду цивільні позови до боржника, щодо якого відкрито провадження про неплатоспроможність?</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/d2b616560dee70ecf11913c9f3f3ab6f.rtf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>124185376</t>
+          <t>128307297</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>910/14329/24</t>
+          <t>905/33/25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1909,319 +1927,319 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Чи є картка рахунку належним доказом виконання робіт за договором підряду за відсутності підписаного акту?</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/e933885ff484c7c8d4fe284d0f903f93.rtf</t>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Чи потрібно подавати окрему заяву про відеоконференцію, якщо суд вже надав дозвіл на участь у всіх засіданнях?</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/600d8d11b4baba6c21bb7a2115873774.rtf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>124186267</t>
+          <t>129566081</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>761/4385/20</t>
+          <t>280/6692/25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>870</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Підстави для відмови у задоволенні скарги на бездіяльність державного виконавця щодо вчинення виконавчих дій</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/68d183bb56e8166f5dded110133ceae9.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягає поновленню строк звернення до суду з позовом про перерахунок чорнобильської пенсії за рішенням КСУ?</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/3666d62e1ecb98f4a5e3f574456e5854.rtf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>124176922</t>
+          <t>130920064</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>752/25338/24</t>
+          <t>916/2795/25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Чи можливе встановлення обопільної вини водіїв у ДТП при порушенні правил безпечного бокового інтервалу?</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/b9bc591b5b5bdaacb40a28f0bee8922a.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Чи має право апеляційний суд відкрити провадження без отримання матеріалів справи з суду першої інстанції?</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/2a12dee547c95d2cdf2d74a7dcfb4576.rtf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>124177241</t>
+          <t>126223775</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>761/42085/19</t>
+          <t>922/1090/25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>чи можливе ухвалення додаткового рішення суду, якщо питання розподілу судових витрат не було вирішено в основному рішенні?</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6954d18de37e51a270d2a9e29cdee507.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Які вимоги до змісту декларації про майновий стан членів сім'ї боржника при відкритті провадження про неплатоспроможність?</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/08646cb886362773e1b3f39cff86560c.rtf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>124176954</t>
+          <t>125188755</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>752/26535/24</t>
+          <t>904/578/25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Відповідальність за створення перешкод дорожньому руху під час виконання будівельних робіт спецтехнікою</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6a942e3560e7a1d87ab79b24298aac96.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки залишення позову без руху через помилку в ідентифікаційному коді відповідача в ЄДР?</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/aea684449732cd6bfe9ab44b293a3165.rtf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>124177262</t>
+          <t>131578972</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>761/30647/23</t>
+          <t>926/2853-б/24 (926/2883/25)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Чи підлягає прийняттю зустрічний позов про поділ спільного майна подружжя у справі про спадкування?</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8d3c40241aa64328cd9597b87dd4fad8.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Чи можна стягнути кошти як безпідставне збагачення, якщо договір між сторонами не укладався?</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/f86f7592e1a755ce4355e1fc9320a7ce.rtf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>124177233</t>
+          <t>125588610</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>761/42312/24</t>
+          <t>921/654/24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Чи підлягає поверненню позовна заява за клопотанням позивача до відкриття провадження у справі?</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/3d5404492db5850ed54cf1f782e9a998.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Чи можливий перехід зі спрощеного до загального позовного провадження після подання зустрічного позову в господарському суді?</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/12d7c402fd552d320d8b963db43d0021.rtf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>124178074</t>
+          <t>127159443</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>368/1155/23</t>
+          <t>922/4444/23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню рішення у справах про стягнення аліментів на утримання непрацездатних батьків?</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/06ada10a11ae475576fb35ace1ff9b97.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>чи можливе відкладення підсумкового засідання у справі про неплатоспроможність фізичної особи за клопотанням боржника?</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/615ea622197594ab5c50040bda7b51b4.rtf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>124178073</t>
+          <t>126944304</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>225/3164/21</t>
+          <t>914/2351/24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Чи підлягають касаційному оскарженню судові рішення у справах про звільнення від сплати аліментів?</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/484f25a93a356bf48acf7bad06e9463c.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Чи має право прокурор оскаржити ухвалу про затвердження мирової угоди, якщо він не брав участі у її укладенні?</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/3bde90fca79b9b3f4f0adf8c2e4be5b0.rtf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>124176943</t>
+          <t>127420954</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>752/25975/24</t>
+          <t>927/794/23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Відповідальність за ст. 124 КУпАП при наїзді на припарковане авто під час руху заднім ходом</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/c443068c94e59b9500d70dbd3bb46566.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірна відмова суду в проведенні відеоконференції через відсутність вільних залів відеозв'язку?</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/842591a7aa58acca92691e408a727387.rtf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>124185312</t>
+          <t>130857753</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>908/2123/23(908/3031/24)</t>
+          <t>904/5490/25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2229,255 +2247,255 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Чи підлягає позов про скасування реєстрації іпотеки розгляду в межах справи про банкрутство боржника?</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/95d537fabbe1693e1fc1e4324b36f1e8.rtf</t>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Як стягнути інфляційні втрати та 3% річних за договором поставки при простроченні оплати товару?</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/0bc10ae898fb7315811cfa3028eea00c.rtf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>124177256</t>
+          <t>126681254</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>758/4169/24</t>
+          <t>911/291/25</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Як зупинити стягнення за виконавчим написом нотаріуса шляхом забезпечення позову про визнання його таким, що не підлягає виконанню?</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/17a4340917c4eaf2d7d665cf7e462e91.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Який порядок подання клопотання про участь у судовому засіданні в режимі відеоконференції поза межами приміщення суду?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/18ce57b540526773ce5c0e73d6814bf0.rtf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>124182855</t>
+          <t>125946380</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>530/2691/24</t>
+          <t>926/814/25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Який порядок визнання права на земельну частку (пай) у судовому порядку після смерті власника?</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/eab7b6e450f8cbb8efb79a7f965f6787.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірна відмова суду у задоволенні клопотання про участь у всіх майбутніх судових засіданнях в режимі відеоконференції?</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/db511f954347fef0f5148bd438dd8852.rtf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>124182861</t>
+          <t>131940295</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>530/2537/24</t>
+          <t>921/677/22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Які процесуальні наслідки неподання відповідачем відзиву на позов у встановлений судом строк?</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/0d012e4e17152fc85f7d6d19d13ec765.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Які підстави для поновлення провадження у справі після усунення обставин, що зумовили його зупинення?</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/620c10cdd787b369b342c55a7c69ff6e.rtf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>124177244</t>
+          <t>125188770</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>635/11525/23</t>
+          <t>904/5362/24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>civil</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Який порядок заміни стягувача у виконавчому провадженні на підставі договору відступлення права вимоги?</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/deaf3e0bd5718f657d0a32a37a83b1e8.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Які підстави стягнення заборгованості за договором оренди після його припинення за взаємною згодою сторін?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/0a277485ce9f07b2547ab00b7a4920f5.rtf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>124176990</t>
+          <t>125910030</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>753/7823/24</t>
+          <t>921/113/25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Яка відповідальність за порушення правил адміністративного нагляду, зокрема відвідування закладів, де продають алкоголь?</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/2ce84ef001bf9bb98ddfcd550a207795.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки часткового усунення недоліків позовної заяви, якщо суд вимагав надати банківські виписки по кредиту?</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/4a2f9b7dd0856e3b908074e618a4e1cd.rtf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>124176895</t>
+          <t>131493608</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>752/24822/24</t>
+          <t>916/4415/25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Відповідальність за ст. 124 КУпАП при ДТП під час руху заднім ходом без забезпечення безпеки маневру</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/dd9c4284d2938a93630cd2535a7751b1.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягають стягненню пеня та інфляційні втрати при простроченні оплати за договором постачання природного газу?</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/f2452ee4239ef90b241fc1c6ba4af3be.rtf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>124176885</t>
+          <t>129960105</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>752/21839/24</t>
+          <t>906/1075/25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Чи можливий розгляд справи про порушення порядку розрахунків за ст. 155-1 КУпАП без присутності продавця?</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/ca9ca5715c2ff054048ca85a0001ed89.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Чи має право прокурор стягувати заборгованість з орендної плати за землю в інтересах органу місцевого самоврядування?</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/0c43a3c98b8ca96fcb203ebebf20eb01.rtf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>124185074</t>
+          <t>130680652</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>910/9177/24</t>
+          <t>914/2429/25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2485,927 +2503,927 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Який розмір судового збору за подання апеляційної скарги через Електронний суд у господарському процесі?</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/2850395cf0febfd314cfef08ed8d0d2f.rtf</t>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірне стягнення інфляційних та 3% річних за договором підряду при простроченні оплати виконаних робіт?</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/8691328a205c0e00158172cdf6d1c9fe.rtf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>124179958</t>
+          <t>129772613</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>518/2358/24</t>
+          <t>914/2341/25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Чи є підставою для відповідальності за ст. 184 КУпАП травмування дитини через відсутність нагляду батьків?</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/9867d55101cf900f81aa75ecdcd62a9d.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Чи є обов'язковою явка представника відповідача у підготовче засідання та наслідки її ігнорування?</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/b3496ec1552697b49daf8aa00e1d1eca.rtf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>124179731</t>
+          <t>124998658</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>522/23352/24</t>
+          <t>910/12610/24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Чи є правомірним розірвання договору в односторонньому порядку без попереднього письмового повідомлення іншої сторони?</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6559746e5e8ff24608835cd1b1d8aa2c.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Чи припиняються зобов'язання за договором поставки автоматично після закінчення строку його дії, якщо сторони продовжували виконання?</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/c2205ec6a488b7ac6906f399bde76d24.rtf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>124179705</t>
+          <t>129056137</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>607/26310/24</t>
+          <t>909/692/24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Які докази є достатніми для притягнення до відповідальності за психологічне домашнє насильство без фізичних ушкоджень?</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/89b8a899c0afdfc1e685cc560f0f93ca.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>Чи вважається касаційна скарга поданою вчасно, якщо недоліки усунуто після відмови у відстроченні судового збору?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/39ae595f5ef4b277e9b03105f65e4775.rtf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>124179205</t>
+          <t>132826193</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>466/884/24</t>
+          <t>914/3060/25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Чи підлягають об'єднанню в одне провадження справи за ст. 124 та ст. 130 КУпАП?</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/31eca50bc5eaa7740d92818063aff901.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки залишення апеляційної скарги без руху через несплату судового збору та порядок його усунення?</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/bbc8f36549315543b6cfe60b08133bf8.rtf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>124178047</t>
+          <t>128772858</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>759/11610/23</t>
+          <t>909/804/25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>процесуальний порядок призначення апеляційного розгляду після відкриття провадження за скаргою обвинуваченого</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/6759bffee8ed5e0f4ab1f5976a1e1798.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>Які документи підтверджують припинення погашення кредитів для відкриття провадження у справі про неплатоспроможність фізичної особи?</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/20d5ac31369c22318079178772cd2723.rtf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>124176474</t>
+          <t>131423153</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>563/2123/24</t>
+          <t>905/638/25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Чи можливо виправити технічну описку в резолютивній частині вироку щодо кваліфікації кримінального правопорушення?</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/75941496c352a5b3d81f98a0b5b0972c.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>Чи є масове подання та відкликання ідентичних позовів зловживанням процесуальними правами, що тягне за собою накладення штрафу?</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/adde20b0b63efd939e4ea240f0ffb42e.rtf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>124178048</t>
+          <t>128166540</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>760/24553/24</t>
+          <t>920/33/25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>процесуальний порядок призначення апеляційного розгляду кримінального провадження за ч 4 ст 191 КК України</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/df07abcb4b03f8c23995b9e8d4954f71.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>Які документи підтверджують повноваження представника юридичної особи для підписання апеляційної скарги в господарському процесі?</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/5420045a00d14eb7da0bea8d5c92338b.rtf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>124176565</t>
+          <t>126866180</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>569/25409/24</t>
+          <t>920/1061/23(920/302/25)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Чи обов'язкове підготовче засідання, якщо в обвинувальному акті щодо кримінального проступку відсутнє клопотання про спрощений розгляд?</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/19c1052c81bf7c16d165b59e15d34b8e.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>Чи зобов'язаний власник квартири з індивідуальним опаленням оплачувати послуги з централізованого опалення місць загального користування?</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/a947388e0b2d1babbb54064e785918fd.rtf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>124182926</t>
+          <t>130492396</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>554/13052/24</t>
+          <t>910/11940/25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Які підстави для накладення арешту на тимчасово вилучене майно як речовий доказ у кримінальному провадженні?</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/e638cfcb161ba08c5bfa9cbde01a60fb.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>Чи можна заборонити орендодавцю чинити перешкоди у доступі до приміщення як захід забезпечення позову до подання позову?</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/41ab9a1b6cb5ff6744f25bc70b4af042.rtf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>124176581</t>
+          <t>126392938</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>569/18131/24</t>
+          <t>923/1092/17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Як застосувати закон про декриміналізацію дрібних крадіжок до вироку, якщо вартість майна не перевищує 2 неоподатковуваних мінімумів?</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/a117ff8151cf2afa2fc86cda4e5138b4.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Які докази оплати за договором відступлення права вимоги необхідні для заміни стягувача у виконавчому провадженні?</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/4955037a4c69c20f5ec42023341e302c.rtf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>124176648</t>
+          <t>128345821</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>357/5072/23</t>
+          <t>914/707/25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Звільнення від покарання за крадіжку у зв'язку з декриміналізацією дрібних крадіжок за законом № 3886-IX?</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/a8b860ddb5d12c84febc5aeb1fe17997.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>Який порядок визнання грошових вимог кредиторів у процедурі неплатоспроможності фізичної особи та підстави для відкладення попереднього засідання?</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/80b2566f69af609e194ff2bb5dd5fd90.rtf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>124182872</t>
+          <t>130407616</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>552/9020/24</t>
+          <t>904/3827/25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Які критерії визначення розміру застави для підозрюваного у тяжкому злочині, якщо захист не надав доказів майнової неспроможності?</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/befdb1b01807b51e515ece5e8e457ef4.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Чи є договір про надання правничої допомоги належним доказом повноважень адвоката без доданого ордера в апеляції?</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/14a89b859fdd258651e17325d1b2b0dd.rtf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>124176579</t>
+          <t>125585419</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>569/13624/23</t>
+          <t>904/744/25</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Як виключити епізод крадіжки з вироку через декриміналізацію дрібних крадіжок згідно із Законом № 3886-IX?</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/afa65b8b5a12383eb06f639bd63fe21d.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>Чи можливо стягнути заборгованість за договором надання послуг через наказне провадження у господарському суді?</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/feba7b5bdaefa61fa9c4b6a344feb1d6.rtf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>124176575</t>
+          <t>125223819</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>569/14919/19</t>
+          <t>914/1200/21(914/133/25)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Як звільнити засудженого від покарання за крадіжку через декриміналізацію діяння згідно із законом № 3886-ІХ?</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/0f02aa3fc493058a1c11f0e5b1c73d1e.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>Чи обов'язковий перехід до загального позовного провадження при прийнятті зустрічного позову у справі про банкрутство?</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/bfdc6961e1831e440fddd4350b68e5fb.rtf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>124176647</t>
+          <t>132387750</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>695/3390/23</t>
+          <t>910/3811/25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Як переглянути вирок через декриміналізацію крадіжки після підвищення порогу кримінальної відповідальності за дрібне викрадення?</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/39a30ed741d6dc6fdb8cd82a2c8595ba.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Який порядок подання клопотання про участь у судовому засіданні в режимі відеоконференції поза межами приміщення суду?</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/66/d542fe63d5f19c41fd429ac2600d8214.rtf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>124176082</t>
+          <t>130595984</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>201/16320/24</t>
+          <t>910/9106/25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Підстави для відмови слідчого судді у застосуванні запобіжного заходу у вигляді тримання під вартою</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8b5de4336313d3756e4f886f317182fd.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>Які підстави для витребування доказів у відповідача та продовження строку підготовчого провадження у господарському процесі?</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/c1a8ac07ea8e2eca7953e3e904ab142f.rtf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>124178465</t>
+          <t>127159185</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>127/40798/24</t>
+          <t>916/3130/21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Підстави для відмови у застосуванні тримання під вартою за підозрою у вимаганні за ч. 4 ст. 189 КК</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/d792902f507bdec0583bde37f173d1d3.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки неявки учасників справи у судове засідання, якщо суд визнав їхню явку обов'язковою?</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/a08dd9705b5fe1620484afc16d041b18.rtf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>124176450</t>
+          <t>131126680</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>556/3606/24</t>
+          <t>910/12486/25</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Чи можна виділити матеріали кримінального провадження в окреме провадження, якщо угоду про визнання винуватості укладено лише з одним обвинуваченим?</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/89ec046f49b00f206f6bf433f193e427.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Які підстави для розірвання договору поставки в судовому порядку при порушенні умов контрагентом?</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/c0894c9d26e73baf8888aa3a6846834a.rtf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>124185969</t>
+          <t>124982908</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>426/2628/14-к</t>
+          <t>140/10431/24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Чи є обов'язковою участь захисника при розгляді заяви про продовження примусових заходів медичного характеру?</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/d79c8ee9f62c73a7236de400dddc009e.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>Чи можливий апеляційний розгляд справи за позовом до Пенсійного фонду у порядку письмового провадження?</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/405fff5a0b4a6fd71bba3e0361e9285c.rtf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>124176680</t>
+          <t>130905758</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>638/4213/24</t>
+          <t>140/8438/25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>процедура оскарження постанови слідчого про закриття кримінального провадження та витребування матеріалів справи</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/62f176866bdae64ba228a24f7c189a1d.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>Чи є підставою для витребування паперової справи подання апеляційної скарги безпосередньо до суду апеляційної інстанції?</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/1e1f4c28caaee94dff1bfb87385575b2.rtf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>124176558</t>
+          <t>129161486</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>569/17179/19</t>
+          <t>440/10209/25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Як привести вирок у відповідність до закону, якщо крадіжка декриміналізована через підвищення порогу дрібного викрадення?</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/22846628bce0c9c220e3d4235c4f46c7.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>Чи правомірна відмова ПФУ у перерахунку пенсії із застосуванням показника середньої зарплати за три попередні роки?</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/8c4a0a96bda0bad09a6f201c60fa491a.rtf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>124187105</t>
+          <t>131869903</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>208/14301/24</t>
+          <t>460/5193/25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Чи можна накласти арешт на вилучений речовий доказ із передачею права користування власнику?</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/a17a1588ce04120e57d5e3c22f7c6811.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Чи можливо продовжити строк розгляду адміністративної справи понад встановлені законом 15 днів через воєнний стан?</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/a5c95c405c931c81ab7114dbed2b8762.rtf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>124179691</t>
+          <t>125244063</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>607/27552/24</t>
+          <t>160/33840/24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>criminal</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Чи можливо визначити заставу при продовженні тримання під вартою у справах про наркозлочини в складі організованої групи?</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/79f4f0f00dad11331e18822a9c3c03dd.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Які вимоги до оформлення відзиву на апеляційну скаргу Пенсійного фонду в адміністративному процесі?</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/1fbd4878bf8c0c4c03ef31355ae18dea.rtf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>124185648</t>
+          <t>128803505</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>922/4759/24</t>
+          <t>160/10684/25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Підстави для відмови в арешті частки ТОВ при позові про переведення прав покупця корпоративних прав</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/0bd627bce731cde71bb8ab443dbf4440.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>процедура витребування матеріалів справи судом апеляційної інстанції після подання скарги через Електронний суд</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/0e80fd5f0474929cbddd5e36ed6f7d94.rtf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>124185653</t>
+          <t>125579087</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>922/3672/21</t>
+          <t>560/3395/25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Чи можна виключити частку в статутному капіталі з ліквідаційної маси боржника за ст. 132 КУзПБ?</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/3eb7b812ca12f84eb010391c6e03118b.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Оскарження відмови Пенсійного фонду у призначенні пенсії: підстави для позову та процедура розгляду</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/fd3ccb7812100634b2a45f89667a526c.rtf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>124185099</t>
+          <t>129759245</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>922/1675/24</t>
+          <t>160/8954/25</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Як правильно розрахувати судовий збір за апеляційну скаргу в справі про банкрутство при подачі через Електронний суд?</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8ef014c9c5c335de8a52e1730ea971b2.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>Підстави для розгляду адміністративної справи в суді апеляційної інстанції в порядку письмового провадження</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/b3d336ffcf9da3b43620006f46b65bc0.rtf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>124185733</t>
+          <t>130249845</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>925/1240/21</t>
+          <t>440/3822/25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Чи є скасування ухвали суду вищою інстанцією підставою для відводу судді згідно з ГПК України?</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/49741bca89bfeba87a45fae30b9da5da.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>Чи підлягає зміні додаткове рішення суду про розподіл судових витрат при залишенні апеляційної скарги без задоволення?</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/ff5bf4bf8025398b02ced847fc95a51f.rtf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>124185415</t>
+          <t>128704736</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>912/3817/19</t>
+          <t>440/14931/24</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Підстави для зупинення провадження у справі до набрання законної сили рішенням в іншій пов'язаній справі</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/c9e1b4f951731ccffefecd23f52d4604.rtf</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>Підстави для скасування податкового повідомлення-рішення в адміністративному суді: судова практика</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/a324c36df5f76117ccabfe39991b9bce.rtf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>124185284</t>
+          <t>129890528</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>908/3001/24</t>
+          <t>910/8753/25</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3413,31 +3431,31 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Чи можливо повернутися до підготовчого провадження після його закриття для залучення третьої особи у господарському процесі?</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8fafacf167dcebda85b94ff39458f622.rtf</t>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Які наслідки повторної неявки позивача в підготовче засідання без поважних причин у господарському процесі?</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/f74ef49c32b76a29c65d7c3198b5ff91.rtf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>124185342</t>
+          <t>126287370</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>909/171/24</t>
+          <t>915/100/25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3445,206 +3463,206 @@
           <t>commercial</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Чи є клопотання арбітражного керуючого про відкладення розгляду справи для узгодження плану реструктуризації підставою для відкладення засідання?</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/57dbaea1434495c8f11bf4daac1e0f1f.rtf</t>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>Чи є воєнний стан підставою для відкладення підготовчого засідання та продовження строків розгляду господарської справи?</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/63/68aaa27db9f3bf46329ae301aa6103bf.rtf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>124187554</t>
+          <t>130528417</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>216/5342/24</t>
+          <t>910/9405/25</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Чи можна поновити провадження у справі про ДТП після надходження висновку судової автотехнічної експертизи?</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/0465308d4fa59918d82f6a4b3056623c.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>процесуальні наслідки оголошення перерви у підготовчому засіданні господарського суду</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/5874d518eaed7c17e30d4769d4e9586e.rtf</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>124186549</t>
+          <t>131280472</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>190/2368/24</t>
+          <t>914/2308/24</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Які докази психологічного домашнього насильства є достатніми для притягнення до відповідальності за ст. 173-2 КУпАП?</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/585be447b1c227a99f35b62e771ff353.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>Чи може релігійна організація визнати право власності на спадкове майно за заповітом у судовому порядку?</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/1e418b6dc781517cba4e83e0aa14d6bf.rtf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>124186550</t>
+          <t>131493663</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>190/2830/24</t>
+          <t>923/1350/20</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Відповідальність за повторне порушення правил адміністративного нагляду: неявка на реєстрацію до поліції</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/560451aee5cc99139ac8e3e1bbe370a8.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>Чи є підставою для відкладення розгляду справи про банкрутство неявка учасників у судове засідання?</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/65/288bfa53c5af145bae0530ff07b0c013.rtf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>124185902</t>
+          <t>128274723</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>286/4354/24</t>
+          <t>908/1277/21</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Підстави та порядок об'єднання кількох справ про адміністративні правопорушення щодо однієї особи в одне провадження</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/5c9a04d184e3d44de9d4a60b3728c46a.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>Чи має право суд самостійно перенести дату розгляду звіту ліквідатора у справі про банкрутство?</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/64/9fde295bdaefa4c5badc47f1615eb931.rtf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>124186101</t>
+          <t>125290238</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>564/1593/21</t>
+          <t>910/7966/24</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Чи підлягає закриттю справа про адмінправопорушення за ст. 130 КУпАП після спливу строків накладення стягнення?</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/8c442e2746d71449101f4da547fcf8b0.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>Підстави для відстрочення виконання рішення суду про стягнення штрафних санкцій з ФОП через скрутне фінансове становище</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/ef18e73a53860920b47da345b7086f70.rtf</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>124186600</t>
+          <t>124383394</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>638/24684/24</t>
+          <t>908/1953/24</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>infraction</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Чи враховуються пом'якшуючі обставини при призначенні штрафу за ст. 124 КУпАП у справах про ДТП?</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>https://od.reyestr.court.gov.ua/files/62/1936ebb5afc7ff7ba6fc33da0a48b17b.rtf</t>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>Який строк пред'явлення до виконання наказу господарського суду про стягнення судового збору?</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://od.reyestr.court.gov.ua/files/62/aa810cfa54b383c18ec45d10eefb56a1.rtf</t>
         </is>
       </c>
     </row>
